--- a/human_validation/judge/kor/judge_D016_S003_P002__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D016_S003_P002__llama-3.3-70b-instruct_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B84"/>
+  <dimension ref="A1:B77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,439 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 병원에 오신 걸 환영합니다. 오늘 저를 찾아오시게 된 이유가 무엇인가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 직장에서 자꾸 이런 성가신 생각이 들어서 왔어요. 레이아웃에서 아주 작은 실수를 놓쳤거나, 고객한테 잘못된 버전을 보낸 것 같은 생각이요. 확인해서 괜찮은 것 같아도, 마음이 계속 그 생각으로 돌아가요. 그게 계속 신경 쓰이더라고요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 그런 성가신 생각을 없애려고 뭔가를 반복해서 하시는 게 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 네. 작업물을 제출하기 전에 보통 파일을 다시 열어서 레이어를 비교하고, 다시 저장한 다음, 머릿속으로 디자인 선택 하나하나를 한 번 더 훑어봐요. 하루 종일 그러는 건 아니지만, 확실히 속도가 느려지고 창의적으로 덜 자유롭다는 느낌이 들어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 이런 성가신 생각이나 뭔가를 계속 확인해야 할 것 같은 느낌을, 업무 외에 삶의 다른 영역에서도 경험하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 잘 모르겠어요. 주로 업무에서 느껴져요, 확인하는 게 거기서 나오니까요. 그 외에는 딱히 신경 써서 본 적이 없거나, 같은 방식으로 눈에 띄지는 않아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 이런 성가신 생각과 작업을 확인해야 한다는 압박감이 전반적인 삶의 질이나 큰 고통을 유발한다고 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 모든 걸 망칠 정도는 아니지만, 네, 영향을 미치기 시작했어요. 여전히 업무는 처리하고 있지만, 계속 확인하느라 내부 마감을 몇 번 놓쳤어요. 그리고 뭔가 놓쳐서 크리에이티브 디렉터로 가는 기회에 흠집이 날까 봐 걱정돼서, 좀 더 과감한 디자인 아이디어들을 자제하고 있다는 걸 느껴요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 이런 성가신 생각과 확인 행동이 친구나 가족과의 관계에 어떤 식으로든 영향을 미쳤나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 관계에 크게 영향을 미친다는 느낌은 별로 못 받았어요. 퇴근 후에 가끔 좀 멍하긴 한데, 친구나 가족이 확실하게 영향을 받은 것 같지는 않아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사 질문] 일을 안 하거나 일에 대해 생각하지 않을 때도 불안하거나 초조하다고 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 환자 응답] 잘 모르겠어요. 가끔 좀 긴장되긴 하는데, 일을 떠나 있거나 일 생각을 안 할 때 그게 규칙적으로 나타나는 것 같지는 않아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사의 감별진단] 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사 질문] 완전히 편안한 상태로 일 생각을 안 하고 있을 때도 불안함을 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 환자 응답] 그렇진 않은 것 같아요. 정말 편안하게 있으면서 일 생각을 안 하고 있으면, 딱히 불안함은 느끼지 않아요. 오히려 완전히 쉬고 있는 순간이 언제인지 잘 모를 때가 많다는 거지, 그런 순간에 불안하다고 말하지는 못하겠어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사의 감별진단] 강박장애 (D016) | 배제됨: 범불안장애 (D011)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사 질문] 업무 외의 사회적인 상황이나 다른 사람들과 어울릴 때 자주 불안하다고 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 환자 응답] 그렇지는 않아요. 누구나처럼 조금 의식하게 될 때는 있지만, 그냥 사람들 곁에 있거나 업무 외의 친구들과 얘기한다고 해서 불안함을 느낀 적은 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사의 감별진단] 강박장애 (D016) | 배제됨: 범불안장애 (D011)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사 질문] 업무와 관련 없이 반복적으로 떠오르거나 통제하기 힘든 생각이나 관념이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 환자 응답] 잘 모르겠어요. 업무와 관련 없는 그런 반복적인 생각은 딱히 떠오르지 않아요. 침투적이거나 통제할 수 없다고 느껴지는 건 없는 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사의 감별진단] 강박장애 (D016) | 배제됨: 범불안장애 (D011)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사 질문] 업무와 관련 없는 생각이 계속 반복되는 것처럼 느껴지신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 환자 응답] 아니요, 그런 것 같지 않아요. 업무와 관련 없는 생각이 머릿속에서 맴도는 걸 느낀 적은 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사의 감별진단] 강박장애 (D016) | 배제됨: 범불안장애 (D011)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사 질문] 일상적인 활동을 하다가 특별한 이유 없이 불안함을 자주 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 환자 응답] 그렇지는 않아요. 보통 하루 중에 이유 없이 불안한 건 아니에요. 불안하다면 대개 뚜렷한 이유가 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사의 감별진단] 강박장애 (D016) | 배제됨: 범불안장애 (D011)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사 질문] 업무와 관련 없는 생각인데 원치 않거나 떨쳐내기 힘든 느낌이 드는 게 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 환자 응답] 아니요, 그런 건 없는 것 같아요. 업무 외에 계속 남아 있거나 떨쳐낼 수 없는 원치 않는 생각은 못 느꼈어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사의 감별진단] 강박장애 (D016) | 배제됨: 범불안장애 (D011)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사 질문] 업무와 관련된 것뿐만 아니라 일반적으로 여러 가지에 대해 불안함을 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 환자 응답] 일반적으로는 아니에요. 실제로 이유가 있으면 걱정하긴 하는데, 모든 것에 대해서나 별다른 뚜렷한 이유 없이 매일매일 불안한 건 아니에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사의 감별진단] 강박장애 (D016) | 배제됨: 범불안장애 (D011)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 의사 질문] 이런 성가신 생각과 확인 행동이 여가 시간을 즐기거나 관계를 유지하는 데 상당한 지장을 주고 있다고 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 환자 응답] 관계나 여가 시간보다는요. 제가 가장 많이 느끼는 곳은 업무예요. 여전히 일은 처리하고 있지만, 내부 마감을 놓치기 시작했고, 뭔가 중요한 걸 놓칠까 봐 걱정돼서 좀 더 과감한 디자인 아이디어를 자제하고 있어요. 그게 크리에이티브 디렉터로 나아가는 기회를 해칠까 봐 걱정돼요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 의사의 감별진단] 강박장애 (D016) | 배제됨: 범불안장애 (D011)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 의사 질문] 업무뿐만 아니라 삶의 폭넓은 영역에 대해 걱정하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 환자 응답] 아니요, 폭넓다고는 말 못하겠어요. 보통 제 삶 전체나 여러 다른 영역에 대해 걱정하지는 않아요. 그보다는 그런 일이 생길 때 좀 더 구체적이에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 의사의 감별진단] 강박장애 (D016) | 배제됨: 범불안장애 (D011)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 의사 질문] 특별한 이유나 상황이 없는데도 불안함을 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 환자 응답] 그렇지 않은 것 같아요. 이유 없이 불안함이 그냥 올라오는 건 딱히 못 느꼈어요. 보통 뭔가 구체적인 것과 연결되어 있는 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 의사의 감별진단] 강박장애 (D016) | 배제됨: 범불안장애 (D011)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 의사 질문] 업무 외에 건강, 재정, 인간관계 같은 것들에 대해 불안함을 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 환자 응답] 그렇지는 않아요. 그러니까, 이런저런 평범한 걱정거리는 있지만, 건강이나 돈, 관계에 대해 특별히 불안하다고 느낀 적은 없어요. 불안이 거기서 오는 것 같지는 않아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 의사의 감별진단] 강박장애 (D016) | 배제됨: 범불안장애 (D011)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 의사 질문] 불안해질 만한 뚜렷한 이유가 없는 상황에서도 불안함을 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 환자 응답] 아니요, 그렇지 않은 것 같아요. 제가 불안하다면 보통 뭔가 구체적인 걸 짚을 수 있어요. 별다른 이유 없이 그런 일이 잘 일어나지는 않아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 의사의 감별진단] 강박장애 (D016) | 배제됨: 범불안장애 (D011)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 의사 질문] 이런 성가신 생각과 확인 행동이 직장 밖에서의 전반적인 삶의 질에 영향을 미치고 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 환자 응답] 주로 업무 쪽에 영향을 미치고, 나머지 삶에는 덜해요. 여전히 일은 처리하고 있지만, 내부 마감을 몇 번 놓치기 시작했어요. 그리고 뭔가 중요한 걸 놓쳐서 크리에이티브 디렉터로 가는 기회를 해칠까 봐 좀 더 크고 과감한 디자인 아이디어를 자제하고 있다는 걸 느껴요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 의사의 감별진단] 강박장애 (D016) | 배제됨: 범불안장애 (D011)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>[20번째 턴 · 의사 질문] 이런 성가신 생각과 확인 행동이 전반적인 행복이나 삶의 만족도에 상당한 영향을 미친다고 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>[20번째 턴 · 환자 응답] 전반적인 행복을 망치는 건 아니에요, 아니요. 하지만 답답하긴 해요. 여전히 일은 하고 있지만, 내부 마감을 놓치고 좀 더 큰 디자인 아이디어를 자제하다 보니 제가 원하는 방향으로, 특히 크리에이티브 디렉터 쪽으로 나아가지 못하고 있다는 느낌이 들어요. 그래서 주로 업무 쪽으로 제 만족도에 영향을 미쳐요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>[20번째 턴 · 의사의 감별진단] 강박장애 (D016) | 배제됨: 범불안장애 (D011)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
         <is>
           <t>진단명: 강박장애 (D016)
 인구통계: 성별 여성 / 나이 40 / 직업상태 designer / 최종학력 학사
@@ -575,488 +999,31 @@
 증상 지속 기간: None
 추가 요건: 
 주호소 증상 코드: S065
-배경 서술: 소피아는 긴장감이 감돌던 고객 인수인계 시기에 디자인 회사에서 해고당한 후, 그 상실을 모든 시안과 파일, 프레젠테이션을 아주 사소한 실수로부터도 지켜내야 한다는 경고로 받아들였다. 처음에는 이것이 직업적인 성실함처럼 보였지만, 자신의 작업에 대한 침투적인 의심이 반복적인 재검토와 재저장, 그리고 그 단계들이 과하다는 걸 알면서도 머릿속으로 디자인 결정을 다시 되짚는 행동을 촉발하기 시작했다. 그녀는 여전히 디자이너로 일하고 있었지만, 이 패턴은 점차 그녀의 창의적인 자유로움을 좁혔고 마감을 힘들게 만들었으며, 크리에이티브 디렉터 자리를 향한 도전을 점점 더 불안하게 느껴지게 만들었다. 요가와 정원 가꾸기, 갤러리 방문처럼 평소에 스트레스를 풀던 방법들이 더 이상 업무상의 의식적인 행동들이 일에 지장을 주는 걸 막기에 충분하지 않다는 걸 깨달은 후, 소피아는 스스로 정신과 진료를 받기로 했다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 병원에 오신 걸 환영합니다. 오늘 저를 찾아오시게 된 이유가 무엇인가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 직장에서 자꾸 이런 성가신 생각이 들어서 왔어요. 레이아웃에서 아주 작은 실수를 놓쳤거나, 고객한테 잘못된 버전을 보낸 것 같은 생각이요. 확인해서 괜찮은 것 같아도, 마음이 계속 그 생각으로 돌아가요. 그게 계속 신경 쓰이더라고요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 고확률: 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 그런 성가신 생각을 없애려고 뭔가를 반복해서 하시는 게 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 네. 작업물을 제출하기 전에 보통 파일을 다시 열어서 레이어를 비교하고, 다시 저장한 다음, 머릿속으로 디자인 선택 하나하나를 한 번 더 훑어봐요. 하루 종일 그러는 건 아니지만, 확실히 속도가 느려지고 창의적으로 덜 자유롭다는 느낌이 들어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 고확률: 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 이런 성가신 생각이나 뭔가를 계속 확인해야 할 것 같은 느낌을, 업무 외에 삶의 다른 영역에서도 경험하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 잘 모르겠어요. 주로 업무에서 느껴져요, 확인하는 게 거기서 나오니까요. 그 외에는 딱히 신경 써서 본 적이 없거나, 같은 방식으로 눈에 띄지는 않아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 고확률: 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 이런 성가신 생각과 작업을 확인해야 한다는 압박감이 전반적인 삶의 질이나 큰 고통을 유발한다고 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 모든 걸 망칠 정도는 아니지만, 네, 영향을 미치기 시작했어요. 여전히 업무는 처리하고 있지만, 계속 확인하느라 내부 마감을 몇 번 놓쳤어요. 그리고 뭔가 놓쳐서 크리에이티브 디렉터로 가는 기회에 흠집이 날까 봐 걱정돼서, 좀 더 과감한 디자인 아이디어들을 자제하고 있다는 걸 느껴요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 고확률: 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 이런 성가신 생각과 확인 행동이 친구나 가족과의 관계에 어떤 식으로든 영향을 미쳤나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 관계에 크게 영향을 미친다는 느낌은 별로 못 받았어요. 퇴근 후에 가끔 좀 멍하긴 한데, 친구나 가족이 확실하게 영향을 받은 것 같지는 않아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사의 감별진단] 고확률: 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사 질문] 일을 안 하거나 일에 대해 생각하지 않을 때도 불안하거나 초조하다고 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 환자 응답] 잘 모르겠어요. 가끔 좀 긴장되긴 하는데, 일을 떠나 있거나 일 생각을 안 할 때 그게 규칙적으로 나타나는 것 같지는 않아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사의 감별진단] 고확률: 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사 질문] 완전히 편안한 상태로 일 생각을 안 하고 있을 때도 불안함을 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 환자 응답] 그렇진 않은 것 같아요. 정말 편안하게 있으면서 일 생각을 안 하고 있으면, 딱히 불안함은 느끼지 않아요. 오히려 완전히 쉬고 있는 순간이 언제인지 잘 모를 때가 많다는 거지, 그런 순간에 불안하다고 말하지는 못하겠어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사의 감별진단] 고확률: 강박장애 (D016) | 배제됨: 범불안장애 (D011)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사 질문] 업무 외의 사회적인 상황이나 다른 사람들과 어울릴 때 자주 불안하다고 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 환자 응답] 그렇지는 않아요. 누구나처럼 조금 의식하게 될 때는 있지만, 그냥 사람들 곁에 있거나 업무 외의 친구들과 얘기한다고 해서 불안함을 느낀 적은 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사의 감별진단] 고확률: 강박장애 (D016) | 배제됨: 범불안장애 (D011)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사 질문] 업무와 관련 없이 반복적으로 떠오르거나 통제하기 힘든 생각이나 관념이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 환자 응답] 잘 모르겠어요. 업무와 관련 없는 그런 반복적인 생각은 딱히 떠오르지 않아요. 침투적이거나 통제할 수 없다고 느껴지는 건 없는 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사의 감별진단] 고확률: 강박장애 (D016) | 배제됨: 범불안장애 (D011)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사 질문] 업무와 관련 없는 생각이 계속 반복되는 것처럼 느껴지신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 환자 응답] 아니요, 그런 것 같지 않아요. 업무와 관련 없는 생각이 머릿속에서 맴도는 걸 느낀 적은 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사의 감별진단] 고확률: 강박장애 (D016) | 배제됨: 범불안장애 (D011)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사 질문] 일상적인 활동을 하다가 특별한 이유 없이 불안함을 자주 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 환자 응답] 그렇지는 않아요. 보통 하루 중에 이유 없이 불안한 건 아니에요. 불안하다면 대개 뚜렷한 이유가 있어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사의 감별진단] 고확률: 강박장애 (D016) | 배제됨: 범불안장애 (D011)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사 질문] 업무와 관련 없는 생각인데 원치 않거나 떨쳐내기 힘든 느낌이 드는 게 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 환자 응답] 아니요, 그런 건 없는 것 같아요. 업무 외에 계속 남아 있거나 떨쳐낼 수 없는 원치 않는 생각은 못 느꼈어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사의 감별진단] 고확률: 강박장애 (D016) | 배제됨: 범불안장애 (D011)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사 질문] 업무와 관련된 것뿐만 아니라 일반적으로 여러 가지에 대해 불안함을 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 환자 응답] 일반적으로는 아니에요. 실제로 이유가 있으면 걱정하긴 하는데, 모든 것에 대해서나 별다른 뚜렷한 이유 없이 매일매일 불안한 건 아니에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사의 감별진단] 고확률: 강박장애 (D016) | 배제됨: 범불안장애 (D011)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 의사 질문] 이런 성가신 생각과 확인 행동이 여가 시간을 즐기거나 관계를 유지하는 데 상당한 지장을 주고 있다고 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 환자 응답] 관계나 여가 시간보다는요. 제가 가장 많이 느끼는 곳은 업무예요. 여전히 일은 처리하고 있지만, 내부 마감을 놓치기 시작했고, 뭔가 중요한 걸 놓칠까 봐 걱정돼서 좀 더 과감한 디자인 아이디어를 자제하고 있어요. 그게 크리에이티브 디렉터로 나아가는 기회를 해칠까 봐 걱정돼요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 의사의 감별진단] 고확률: 강박장애 (D016) | 배제됨: 범불안장애 (D011)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 의사 질문] 업무뿐만 아니라 삶의 폭넓은 영역에 대해 걱정하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 환자 응답] 아니요, 폭넓다고는 말 못하겠어요. 보통 제 삶 전체나 여러 다른 영역에 대해 걱정하지는 않아요. 그보다는 그런 일이 생길 때 좀 더 구체적이에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 의사의 감별진단] 고확률: 강박장애 (D016) | 배제됨: 범불안장애 (D011)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 의사 질문] 특별한 이유나 상황이 없는데도 불안함을 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 환자 응답] 그렇지 않은 것 같아요. 이유 없이 불안함이 그냥 올라오는 건 딱히 못 느꼈어요. 보통 뭔가 구체적인 것과 연결되어 있는 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 의사의 감별진단] 고확률: 강박장애 (D016) | 배제됨: 범불안장애 (D011)</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="B66" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 의사 질문] 업무 외에 건강, 재정, 인간관계 같은 것들에 대해 불안함을 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 환자 응답] 그렇지는 않아요. 그러니까, 이런저런 평범한 걱정거리는 있지만, 건강이나 돈, 관계에 대해 특별히 불안하다고 느낀 적은 없어요. 불안이 거기서 오는 것 같지는 않아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="B68" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 의사의 감별진단] 고확률: 강박장애 (D016) | 배제됨: 범불안장애 (D011)</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 의사 질문] 불안해질 만한 뚜렷한 이유가 없는 상황에서도 불안함을 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 환자 응답] 아니요, 그렇지 않은 것 같아요. 제가 불안하다면 보통 뭔가 구체적인 걸 짚을 수 있어요. 별다른 이유 없이 그런 일이 잘 일어나지는 않아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 의사의 감별진단] 고확률: 강박장애 (D016) | 배제됨: 범불안장애 (D011)</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="B72" s="5" t="inlineStr">
-        <is>
-          <t>[19번째 턴 · 의사 질문] 이런 성가신 생각과 확인 행동이 직장 밖에서의 전반적인 삶의 질에 영향을 미치고 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>[19번째 턴 · 환자 응답] 주로 업무 쪽에 영향을 미치고, 나머지 삶에는 덜해요. 여전히 일은 처리하고 있지만, 내부 마감을 몇 번 놓치기 시작했어요. 그리고 뭔가 중요한 걸 놓쳐서 크리에이티브 디렉터로 가는 기회를 해칠까 봐 좀 더 크고 과감한 디자인 아이디어를 자제하고 있다는 걸 느껴요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="B74" s="5" t="inlineStr">
-        <is>
-          <t>[19번째 턴 · 의사의 감별진단] 고확률: 강박장애 (D016) | 배제됨: 범불안장애 (D011)</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="B75" s="5" t="inlineStr">
-        <is>
-          <t>[20번째 턴 · 의사 질문] 이런 성가신 생각과 확인 행동이 전반적인 행복이나 삶의 만족도에 상당한 영향을 미친다고 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t>[20번째 턴 · 환자 응답] 전반적인 행복을 망치는 건 아니에요, 아니요. 하지만 답답하긴 해요. 여전히 일은 하고 있지만, 내부 마감을 놓치고 좀 더 큰 디자인 아이디어를 자제하다 보니 제가 원하는 방향으로, 특히 크리에이티브 디렉터 쪽으로 나아가지 못하고 있다는 느낌이 들어요. 그래서 주로 업무 쪽으로 제 만족도에 영향을 미쳐요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
+배경 서술: 소피아는 긴장감이 감돌던 고객 인수인계 시기에 디자인 회사에서 해고당한 후, 그 상실을 모든 시안과 파일, 프레젠테이션을 아주 사소한 실수로부터도 지켜내야 한다는 경고로 받아들였다. 처음에는 이것이 직업적인 성실함처럼 보였지만, 자신의 작업에 대한 침투적인 의심이 반복적인 재검토와 재저장, 그리고 그 단계들이 과하다는 걸 알면서도 머릿속으로 디자인 결정을 다시 되짚는 행동을 촉발하기 시작했다. 그녀는 여전히 디자이너로 일하고 있었지만, 이 패턴은 점차 그녀의 창의적인 자유로움을 좁혔고 마감을 힘들게 만들었으며, 크리에이티브 디렉터 자리를 향한 도전을 점점 더 불안하게 느껴지게 만들었다. 요가와 정원 가꾸기, 갤러리 방문처럼 평소에 스트레스를 풀던 방법들이 더 이상 업무상의 의식적인 행동들이 일에 지장을 주는 걸 막기에 충분하지 않다는 걸 깨달은 후, 소피아는 스스로 정신과 진료를 받기로 했다.
+표집된 증상 목록:
+  - S065 강박사고: 침투적이고 원치 않는 것으로 경험되는 반복적이고 지속적인 생각, 충동, 심상, 그리고 이를 무시하거나 억누르려는 시도.
+  - S066 강박행동: 강박사고에 대한 반응으로, 또는 불안/고통을 예방하기 위해 수행하는 반복적 행동이나 정신적 활동으로, 명백히 과도하거나 현실적으로 연관성이 없음.</t>
+        </is>
+      </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>[20번째 턴 · 의사의 감별진단] 고확률: 강박장애 (D016) | 배제됨: 범불안장애 (D011)</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 강박장애 (D016, ICD: F42.2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: obsessive_compulsive_symptoms (관계=must_include, 요구개수=1, 충족개수=2, 커버리지=1.0)
-  확인된 근거: 강박사고: 침투적이고 원치 않는 것으로 경험되는 반복적이고 지속적인 생각, 충동, 심상, 그리고 이를 무시하거나 억누르려는 시도.; 강박행동: 강박사고에 대한 반응으로, 또는 불안/고통을 예방하기 위해 수행하는 반복적 행동이나 정신적 활동으로, 명백히 과도하거나 현실적으로 연관성이 없음.
-  누락: (없음)</t>
+          <t>의사의 최종 진단: 강박장애 (D016, ICD: F42.2)
+지속 기간 요건: None
+기능적 손상 요건: 있음
+추가 요건: None
+체크리스트 그룹: obsessive_compulsive_symptoms (관계=must_include, 요구개수=1, 충족개수=2, 커버리지=1.0)
+확인된 근거:
+  - 강박사고: 침투적이고 원치 않는 것으로 경험되는 반복적이고 지속적인 생각, 충동, 심상, 그리고 이를 무시하거나 억누르려는 시도.
+  - 강박행동: 강박사고에 대한 반응으로, 또는 불안/고통을 예방하기 위해 수행하는 반복적 행동이나 정신적 활동으로, 명백히 과도하거나 현실적으로 연관성이 없음.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="A76:B76"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D016_S003_P002__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D016_S003_P002__llama-3.3-70b-instruct_kor.xlsx
@@ -985,6 +985,11 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -1019,11 +1024,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A76:B76"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D016_S003_P002__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D016_S003_P002__llama-3.3-70b-instruct_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.2485</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>1</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
